--- a/Deliverables/BOM/PCBWay_BOM.xlsx
+++ b/Deliverables/BOM/PCBWay_BOM.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25726"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\JohnWollam-LCDProject\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\JohnWollam-LCDProject\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C4283D2-F5CD-46E9-A4C2-92E47DEC178C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -626,9 +625,6 @@
     <t>8MHZ</t>
   </si>
   <si>
-    <t xml:space="preserve"> Quantity (25 Boards)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> MOQ (25 Boards)</t>
   </si>
   <si>
@@ -657,12 +653,15 @@
   </si>
   <si>
     <t>5TJ480000XYLBC</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Quantity per board</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
@@ -1421,7 +1420,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09969436-8A94-45CE-BB95-34EF24CD6072}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{09969436-8A94-45CE-BB95-34EF24CD6072}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1717,7 +1716,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:M42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1746,7 +1745,7 @@
       </c>
       <c r="E2" s="36"/>
       <c r="F2" s="69" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="2"/>
@@ -1764,7 +1763,7 @@
       </c>
       <c r="E3" s="10"/>
       <c r="F3" s="70" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="3"/>
@@ -1782,7 +1781,7 @@
       </c>
       <c r="E4" s="10"/>
       <c r="F4" s="71" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="5"/>
@@ -1881,10 +1880,10 @@
         <v>154</v>
       </c>
       <c r="K9" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="L9" s="23" t="s">
         <v>198</v>
-      </c>
-      <c r="L9" s="23" t="s">
-        <v>199</v>
       </c>
       <c r="M9" s="23" t="s">
         <v>37</v>
@@ -1920,7 +1919,7 @@
         <v>29</v>
       </c>
       <c r="K10" s="48">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L10" s="48">
         <v>200</v>
@@ -1957,7 +1956,7 @@
         <v>30</v>
       </c>
       <c r="K11" s="50">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="L11" s="50">
         <v>100</v>
@@ -1994,7 +1993,7 @@
         <v>32</v>
       </c>
       <c r="K12" s="52">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="L12" s="52">
         <v>60</v>
@@ -2031,7 +2030,7 @@
         <v>159</v>
       </c>
       <c r="K13" s="50">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L13" s="50">
         <v>100</v>
@@ -2068,7 +2067,7 @@
         <v>31</v>
       </c>
       <c r="K14" s="52">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="L14" s="52">
         <v>60</v>
@@ -2105,7 +2104,7 @@
         <v>162</v>
       </c>
       <c r="K15" s="50">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L15" s="50">
         <v>100</v>
@@ -2142,7 +2141,7 @@
         <v>164</v>
       </c>
       <c r="K16" s="52">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L16" s="52">
         <v>28</v>
@@ -2179,7 +2178,7 @@
         <v>166</v>
       </c>
       <c r="K17" s="55">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L17" s="55">
         <v>28</v>
@@ -2216,7 +2215,7 @@
         <v>144</v>
       </c>
       <c r="K18" s="52">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="L18" s="52">
         <v>60</v>
@@ -2253,7 +2252,7 @@
         <v>144</v>
       </c>
       <c r="K19" s="50">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L19" s="50">
         <v>40</v>
@@ -2278,7 +2277,7 @@
         <v>34</v>
       </c>
       <c r="G20" s="62" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H20" s="52" t="s">
         <v>127</v>
@@ -2290,7 +2289,7 @@
         <v>144</v>
       </c>
       <c r="K20" s="52">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L20" s="52">
         <v>28</v>
@@ -2327,7 +2326,7 @@
         <v>144</v>
       </c>
       <c r="K21" s="50">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L21" s="50">
         <v>30</v>
@@ -2352,7 +2351,7 @@
         <v>34</v>
       </c>
       <c r="G22" s="73" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H22" s="52" t="s">
         <v>130</v>
@@ -2364,7 +2363,7 @@
         <v>144</v>
       </c>
       <c r="K22" s="52">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L22" s="52">
         <v>30</v>
@@ -2401,7 +2400,7 @@
         <v>173</v>
       </c>
       <c r="K23" s="50">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L23" s="50">
         <v>28</v>
@@ -2426,7 +2425,7 @@
         <v>34</v>
       </c>
       <c r="G24" s="62" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H24" s="52" t="s">
         <v>35</v>
@@ -2438,7 +2437,7 @@
         <v>144</v>
       </c>
       <c r="K24" s="52">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L24" s="52">
         <v>50</v>
@@ -2463,7 +2462,7 @@
         <v>21</v>
       </c>
       <c r="G25" s="74" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H25" s="50" t="s">
         <v>133</v>
@@ -2475,7 +2474,7 @@
         <v>144</v>
       </c>
       <c r="K25" s="50">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L25" s="50">
         <v>160</v>
@@ -2500,7 +2499,7 @@
         <v>80</v>
       </c>
       <c r="G26" s="65" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H26" s="52" t="s">
         <v>134</v>
@@ -2512,7 +2511,7 @@
         <v>177</v>
       </c>
       <c r="K26" s="52">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="L26" s="52">
         <v>60</v>
@@ -2537,7 +2536,7 @@
         <v>83</v>
       </c>
       <c r="G27" s="74" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H27" s="50" t="s">
         <v>135</v>
@@ -2549,7 +2548,7 @@
         <v>179</v>
       </c>
       <c r="K27" s="50">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L27" s="50">
         <v>50</v>
@@ -2586,7 +2585,7 @@
         <v>181</v>
       </c>
       <c r="K28" s="52">
-        <v>275</v>
+        <v>11</v>
       </c>
       <c r="L28" s="52">
         <v>300</v>
@@ -2623,7 +2622,7 @@
         <v>33</v>
       </c>
       <c r="K29" s="50">
-        <v>325</v>
+        <v>13</v>
       </c>
       <c r="L29" s="50">
         <v>400</v>
@@ -2660,7 +2659,7 @@
         <v>184</v>
       </c>
       <c r="K30" s="52">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L30" s="52">
         <v>100</v>
@@ -2697,7 +2696,7 @@
         <v>186</v>
       </c>
       <c r="K31" s="50">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L31" s="50">
         <v>50</v>
@@ -2734,7 +2733,7 @@
         <v>188</v>
       </c>
       <c r="K32" s="52">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L32" s="52">
         <v>28</v>
@@ -2771,7 +2770,7 @@
         <v>190</v>
       </c>
       <c r="K33" s="50">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L33" s="50">
         <v>100</v>
@@ -2808,7 +2807,7 @@
         <v>144</v>
       </c>
       <c r="K34" s="57">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L34" s="57" t="s">
         <v>144</v>
@@ -2845,7 +2844,7 @@
         <v>144</v>
       </c>
       <c r="K35" s="50">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L35" s="50">
         <v>28</v>
@@ -2882,7 +2881,7 @@
         <v>144</v>
       </c>
       <c r="K36" s="52">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L36" s="52">
         <v>27</v>
@@ -2919,7 +2918,7 @@
         <v>144</v>
       </c>
       <c r="K37" s="50">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L37" s="50">
         <v>27</v>
@@ -2956,7 +2955,7 @@
         <v>144</v>
       </c>
       <c r="K38" s="52">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L38" s="52">
         <v>27</v>
@@ -2993,7 +2992,7 @@
         <v>144</v>
       </c>
       <c r="K39" s="50">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L39" s="50">
         <v>30</v>
@@ -3018,7 +3017,7 @@
         <v>34</v>
       </c>
       <c r="G40" s="52" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H40" s="59" t="s">
         <v>152</v>
@@ -3030,7 +3029,7 @@
         <v>197</v>
       </c>
       <c r="K40" s="59">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L40" s="59">
         <v>30</v>

--- a/Deliverables/BOM/PCBWay_BOM.xlsx
+++ b/Deliverables/BOM/PCBWay_BOM.xlsx
@@ -1,35 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Faizan\GitHub\JohnWollam-LCDProject\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\JohnWollam-LCDProject\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4416249-9589-403F-9480-ABE69A1C5A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="212">
   <si>
     <t>Component list</t>
   </si>
@@ -289,18 +280,12 @@
     <t>RES 20K OHM 1% 1/10W 0603</t>
   </si>
   <si>
-    <t>R18, R20, R21, R22, R23, R24, R25, R26, R27, R28, R29, R30, R31</t>
-  </si>
-  <si>
     <t>RES SMD 10K Ohm 1% 1/10W 0603</t>
   </si>
   <si>
     <t>R19</t>
   </si>
   <si>
-    <t>RES 56K OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
     <t>R32</t>
   </si>
   <si>
@@ -445,9 +430,6 @@
     <t>RC0603FR-0710KL</t>
   </si>
   <si>
-    <t>RC0603FR-0756KL</t>
-  </si>
-  <si>
     <t>RTT03R330FTP</t>
   </si>
   <si>
@@ -580,12 +562,6 @@
     <t>C98220</t>
   </si>
   <si>
-    <t>C114630</t>
-  </si>
-  <si>
-    <t>56K</t>
-  </si>
-  <si>
     <t>C103893</t>
   </si>
   <si>
@@ -652,20 +628,44 @@
     <t>RC1206JR-073R6L</t>
   </si>
   <si>
-    <t>5TJ480000XYLBC</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Quantity per board</t>
+    <t>Terminal Block</t>
+  </si>
+  <si>
+    <t>R18</t>
+  </si>
+  <si>
+    <t>RES SMD 1K OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>RC0603FR-071KL</t>
+  </si>
+  <si>
+    <t>DNP</t>
+  </si>
+  <si>
+    <t>R20, R21, R22, R23, R24, R25, R26, R27, R28, R29, R30, R31</t>
+  </si>
+  <si>
+    <t>7B08070001</t>
+  </si>
+  <si>
+    <t>C22548</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>Quantity per Head</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -827,6 +827,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <strike/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -860,7 +883,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1056,17 +1079,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1108,35 +1120,97 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="medium">
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
@@ -1148,7 +1222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1233,9 +1307,6 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1277,70 +1348,40 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1352,10 +1393,10 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1381,6 +1422,57 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1420,7 +1512,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{09969436-8A94-45CE-BB95-34EF24CD6072}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09969436-8A94-45CE-BB95-34EF24CD6072}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1716,8 +1808,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:M42"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:M43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
@@ -1738,32 +1830,32 @@
       <c r="I1" s="1"/>
     </row>
     <row r="2" spans="2:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="36" t="s">
+      <c r="B2" s="34"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="36"/>
-      <c r="F2" s="69" t="s">
-        <v>199</v>
+      <c r="E2" s="35"/>
+      <c r="F2" s="58" t="s">
+        <v>194</v>
       </c>
       <c r="G2" s="9"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="78"/>
+      <c r="K2" s="66"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="67"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="17"/>
-      <c r="C3" s="39"/>
+      <c r="C3" s="38"/>
       <c r="D3" s="10" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="10"/>
-      <c r="F3" s="70" t="s">
-        <v>200</v>
+      <c r="F3" s="59" t="s">
+        <v>195</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="3"/>
@@ -1771,17 +1863,17 @@
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
-      <c r="M3" s="75"/>
+      <c r="M3" s="64"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" s="17"/>
-      <c r="C4" s="39"/>
+      <c r="C4" s="38"/>
       <c r="D4" s="10" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="10"/>
-      <c r="F4" s="71" t="s">
-        <v>200</v>
+      <c r="F4" s="60" t="s">
+        <v>195</v>
       </c>
       <c r="G4" s="11"/>
       <c r="H4" s="5"/>
@@ -1789,16 +1881,16 @@
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
-      <c r="M4" s="76"/>
+      <c r="M4" s="65"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="17"/>
-      <c r="C5" s="39"/>
+      <c r="C5" s="38"/>
       <c r="D5" s="10" t="s">
         <v>3</v>
       </c>
       <c r="E5" s="10"/>
-      <c r="F5" s="72" t="s">
+      <c r="F5" s="61" t="s">
         <v>7</v>
       </c>
       <c r="G5" s="12"/>
@@ -1807,11 +1899,11 @@
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
-      <c r="M5" s="76"/>
+      <c r="M5" s="65"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="18"/>
-      <c r="C6" s="40"/>
+      <c r="C6" s="39"/>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
       <c r="F6" s="14"/>
@@ -1821,11 +1913,11 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
-      <c r="M6" s="76"/>
+      <c r="M6" s="65"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" s="19"/>
-      <c r="C7" s="41"/>
+      <c r="C7" s="40"/>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
       <c r="F7" s="16"/>
@@ -1835,11 +1927,11 @@
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
-      <c r="M7" s="76"/>
+      <c r="M7" s="65"/>
     </row>
     <row r="8" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="26"/>
-      <c r="C8" s="42"/>
+      <c r="C8" s="41"/>
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
       <c r="F8" s="28"/>
@@ -1849,13 +1941,13 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
-      <c r="M8" s="76"/>
+      <c r="M8" s="65"/>
     </row>
     <row r="9" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="23" t="s">
         <v>43</v>
       </c>
       <c r="D9" s="23" t="s">
@@ -1874,1205 +1966,1242 @@
         <v>23</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="J9" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="K9" s="23" t="s">
-        <v>208</v>
+        <v>151</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>211</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="M9" s="23" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="2:13" s="37" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="45">
+    <row r="10" spans="2:13" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="44">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="48" t="s">
+      <c r="D10" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="48" t="s">
+      <c r="E10" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="48" t="s">
+      <c r="F10" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="48" t="s">
+      <c r="G10" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="H10" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="I10" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="J10" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="K10" s="46">
+        <v>6</v>
+      </c>
+      <c r="L10" s="46">
+        <v>200</v>
+      </c>
+      <c r="M10" s="29"/>
+    </row>
+    <row r="11" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="44">
+        <f t="shared" ref="B11:B41" si="0">ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="80" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="73" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="H11" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="52" t="s">
+        <v>153</v>
+      </c>
+      <c r="J11" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" s="48">
+        <v>2</v>
+      </c>
+      <c r="L11" s="48">
+        <v>100</v>
+      </c>
+      <c r="M11" s="22"/>
+    </row>
+    <row r="12" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="44">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C12" s="81" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="74" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="49" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="49" t="s">
         <v>113</v>
       </c>
-      <c r="H10" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="60" t="s">
-        <v>155</v>
-      </c>
-      <c r="J10" s="48" t="s">
-        <v>29</v>
-      </c>
-      <c r="K10" s="48">
-        <v>6</v>
-      </c>
-      <c r="L10" s="48">
-        <v>200</v>
-      </c>
-      <c r="M10" s="29"/>
-    </row>
-    <row r="11" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="45">
-        <f t="shared" ref="B11:B39" si="0">ROW(B11) - ROW($B$9)</f>
+      <c r="H12" s="49" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="53" t="s">
+        <v>154</v>
+      </c>
+      <c r="J12" s="49" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12" s="49">
         <v>2</v>
       </c>
-      <c r="C11" s="49" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="50" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="50" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" s="50" t="s">
-        <v>114</v>
-      </c>
-      <c r="H11" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="61" t="s">
-        <v>156</v>
-      </c>
-      <c r="J11" s="50" t="s">
-        <v>30</v>
-      </c>
-      <c r="K11" s="50">
-        <v>2</v>
-      </c>
-      <c r="L11" s="50">
-        <v>100</v>
-      </c>
-      <c r="M11" s="22"/>
-    </row>
-    <row r="12" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="45">
-        <f>ROW(B12) - ROW($B$9)</f>
-        <v>3</v>
-      </c>
-      <c r="C12" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="52" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="52" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="52" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" s="52" t="s">
-        <v>115</v>
-      </c>
-      <c r="H12" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12" s="62" t="s">
-        <v>157</v>
-      </c>
-      <c r="J12" s="52" t="s">
-        <v>32</v>
-      </c>
-      <c r="K12" s="52">
-        <v>2</v>
-      </c>
-      <c r="L12" s="52">
+      <c r="L12" s="49">
         <v>60</v>
       </c>
       <c r="M12" s="21"/>
     </row>
     <row r="13" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="45">
+      <c r="B13" s="44">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="49" t="s">
+      <c r="C13" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="50" t="s">
+      <c r="D13" s="73" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="50" t="s">
+      <c r="E13" s="48" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="50" t="s">
+      <c r="F13" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="G13" s="50" t="s">
-        <v>116</v>
-      </c>
-      <c r="H13" s="50" t="s">
+      <c r="G13" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="H13" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="I13" s="61" t="s">
-        <v>158</v>
-      </c>
-      <c r="J13" s="50" t="s">
-        <v>159</v>
-      </c>
-      <c r="K13" s="50">
+      <c r="I13" s="52" t="s">
+        <v>155</v>
+      </c>
+      <c r="J13" s="48" t="s">
+        <v>156</v>
+      </c>
+      <c r="K13" s="48">
         <v>1</v>
       </c>
-      <c r="L13" s="50">
+      <c r="L13" s="48">
         <v>100</v>
       </c>
       <c r="M13" s="22"/>
     </row>
     <row r="14" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="45">
-        <f>ROW(B14) - ROW($B$9)</f>
+      <c r="B14" s="44">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="52" t="s">
+      <c r="D14" s="74" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="52" t="s">
+      <c r="E14" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="F14" s="52" t="s">
+      <c r="F14" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="G14" s="52" t="s">
-        <v>117</v>
-      </c>
-      <c r="H14" s="52" t="s">
+      <c r="G14" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="H14" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="62" t="s">
-        <v>160</v>
-      </c>
-      <c r="J14" s="52" t="s">
+      <c r="I14" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="J14" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="K14" s="52">
+      <c r="K14" s="49">
         <v>2</v>
       </c>
-      <c r="L14" s="52">
+      <c r="L14" s="49">
         <v>60</v>
       </c>
       <c r="M14" s="21"/>
     </row>
     <row r="15" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="45">
+      <c r="B15" s="44">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="49" t="s">
+      <c r="C15" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="50" t="s">
+      <c r="D15" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="50" t="s">
+      <c r="E15" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="50" t="s">
+      <c r="F15" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="G15" s="50" t="s">
+      <c r="G15" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="H15" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="52" t="s">
+        <v>158</v>
+      </c>
+      <c r="J15" s="48" t="s">
+        <v>159</v>
+      </c>
+      <c r="K15" s="48">
+        <v>1</v>
+      </c>
+      <c r="L15" s="48">
+        <v>100</v>
+      </c>
+      <c r="M15" s="22"/>
+    </row>
+    <row r="16" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="44">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C16" s="81" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="49" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="49" t="s">
+        <v>117</v>
+      </c>
+      <c r="H16" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="H15" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="I15" s="61" t="s">
+      <c r="I16" s="53" t="s">
+        <v>160</v>
+      </c>
+      <c r="J16" s="49" t="s">
         <v>161</v>
       </c>
-      <c r="J15" s="50" t="s">
-        <v>162</v>
-      </c>
-      <c r="K15" s="50">
+      <c r="K16" s="49">
         <v>1</v>
       </c>
-      <c r="L15" s="50">
-        <v>100</v>
-      </c>
-      <c r="M15" s="22"/>
-    </row>
-    <row r="16" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="45">
-        <f>ROW(B16) - ROW($B$9)</f>
-        <v>7</v>
-      </c>
-      <c r="C16" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="52" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="52" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="52" t="s">
-        <v>119</v>
-      </c>
-      <c r="H16" s="52" t="s">
-        <v>120</v>
-      </c>
-      <c r="I16" s="62" t="s">
-        <v>163</v>
-      </c>
-      <c r="J16" s="52" t="s">
-        <v>164</v>
-      </c>
-      <c r="K16" s="52">
-        <v>1</v>
-      </c>
-      <c r="L16" s="52">
+      <c r="L16" s="49">
         <v>28</v>
       </c>
       <c r="M16" s="25"/>
     </row>
     <row r="17" spans="2:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="53">
+      <c r="B17" s="44">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="54" t="s">
+      <c r="C17" s="82" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="55" t="s">
+      <c r="D17" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="50" t="s">
+      <c r="E17" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="55" t="s">
+      <c r="F17" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="55" t="s">
+      <c r="G17" s="50" t="s">
+        <v>119</v>
+      </c>
+      <c r="H17" s="50" t="s">
+        <v>120</v>
+      </c>
+      <c r="I17" s="50" t="s">
+        <v>162</v>
+      </c>
+      <c r="J17" s="50" t="s">
+        <v>163</v>
+      </c>
+      <c r="K17" s="50">
+        <v>1</v>
+      </c>
+      <c r="L17" s="50">
+        <v>28</v>
+      </c>
+      <c r="M17" s="22"/>
+    </row>
+    <row r="18" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="44">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C18" s="81" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" s="49" t="s">
+        <v>64</v>
+      </c>
+      <c r="G18" s="49" t="s">
         <v>121</v>
       </c>
-      <c r="H17" s="55" t="s">
+      <c r="H18" s="49" t="s">
         <v>122</v>
       </c>
-      <c r="I17" s="55" t="s">
-        <v>165</v>
-      </c>
-      <c r="J17" s="55" t="s">
-        <v>166</v>
-      </c>
-      <c r="K17" s="55">
-        <v>1</v>
-      </c>
-      <c r="L17" s="55">
-        <v>28</v>
-      </c>
-      <c r="M17" s="22"/>
-    </row>
-    <row r="18" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="45">
-        <f>ROW(B18) - ROW($B$9)</f>
-        <v>9</v>
-      </c>
-      <c r="C18" s="51" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" s="52" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" s="52" t="s">
-        <v>63</v>
-      </c>
-      <c r="F18" s="52" t="s">
-        <v>64</v>
-      </c>
-      <c r="G18" s="52" t="s">
-        <v>123</v>
-      </c>
-      <c r="H18" s="52" t="s">
-        <v>124</v>
-      </c>
-      <c r="I18" s="62" t="s">
-        <v>167</v>
-      </c>
-      <c r="J18" s="52" t="s">
-        <v>144</v>
-      </c>
-      <c r="K18" s="52">
+      <c r="I18" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="J18" s="49" t="s">
+        <v>141</v>
+      </c>
+      <c r="K18" s="49">
         <v>2</v>
       </c>
-      <c r="L18" s="52">
+      <c r="L18" s="49">
         <v>60</v>
       </c>
       <c r="M18" s="25"/>
     </row>
     <row r="19" spans="2:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="45">
+      <c r="B19" s="44">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="49" t="s">
+      <c r="C19" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="50" t="s">
+      <c r="D19" s="73" t="s">
         <v>65</v>
       </c>
-      <c r="E19" s="50" t="s">
+      <c r="E19" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="F19" s="50" t="s">
+      <c r="F19" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="G19" s="50" t="s">
+      <c r="G19" s="48" t="s">
+        <v>123</v>
+      </c>
+      <c r="H19" s="48" t="s">
+        <v>124</v>
+      </c>
+      <c r="I19" s="48" t="s">
+        <v>165</v>
+      </c>
+      <c r="J19" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="K19" s="48">
+        <v>1</v>
+      </c>
+      <c r="L19" s="48">
+        <v>40</v>
+      </c>
+      <c r="M19" s="22"/>
+    </row>
+    <row r="20" spans="2:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="44">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C20" s="81" t="s">
+        <v>202</v>
+      </c>
+      <c r="D20" s="74" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="53" t="s">
+        <v>196</v>
+      </c>
+      <c r="H20" s="49" t="s">
         <v>125</v>
       </c>
-      <c r="H19" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="I19" s="50" t="s">
-        <v>168</v>
-      </c>
-      <c r="J19" s="50" t="s">
-        <v>144</v>
-      </c>
-      <c r="K19" s="50">
+      <c r="I20" s="53" t="s">
+        <v>166</v>
+      </c>
+      <c r="J20" s="49" t="s">
+        <v>141</v>
+      </c>
+      <c r="K20" s="49">
         <v>1</v>
       </c>
-      <c r="L19" s="50">
-        <v>40</v>
-      </c>
-      <c r="M19" s="22"/>
-    </row>
-    <row r="20" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="45">
-        <f>ROW(B20) - ROW($B$9)</f>
-        <v>11</v>
-      </c>
-      <c r="C20" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="52" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="F20" s="52" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" s="62" t="s">
-        <v>201</v>
-      </c>
-      <c r="H20" s="52" t="s">
-        <v>127</v>
-      </c>
-      <c r="I20" s="62" t="s">
-        <v>169</v>
-      </c>
-      <c r="J20" s="52" t="s">
-        <v>144</v>
-      </c>
-      <c r="K20" s="52">
-        <v>1</v>
-      </c>
-      <c r="L20" s="52">
+      <c r="L20" s="49">
         <v>28</v>
       </c>
       <c r="M20" s="25"/>
     </row>
     <row r="21" spans="2:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="45">
+      <c r="B21" s="44">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="49" t="s">
+      <c r="C21" s="80" t="s">
+        <v>202</v>
+      </c>
+      <c r="D21" s="73" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" s="48" t="s">
+        <v>126</v>
+      </c>
+      <c r="H21" s="48" t="s">
+        <v>127</v>
+      </c>
+      <c r="I21" s="48" t="s">
+        <v>167</v>
+      </c>
+      <c r="J21" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="K21" s="48">
+        <v>1</v>
+      </c>
+      <c r="L21" s="48">
+        <v>30</v>
+      </c>
+      <c r="M21" s="22"/>
+    </row>
+    <row r="22" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="44">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C22" s="81" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="50" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="50" t="s">
-        <v>70</v>
-      </c>
-      <c r="F21" s="50" t="s">
+      <c r="D22" s="74" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="49" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="G21" s="50" t="s">
+      <c r="G22" s="62" t="s">
+        <v>197</v>
+      </c>
+      <c r="H22" s="49" t="s">
         <v>128</v>
       </c>
-      <c r="H21" s="50" t="s">
-        <v>129</v>
-      </c>
-      <c r="I21" s="50" t="s">
-        <v>170</v>
-      </c>
-      <c r="J21" s="50" t="s">
-        <v>144</v>
-      </c>
-      <c r="K21" s="50">
+      <c r="I22" s="54" t="s">
+        <v>168</v>
+      </c>
+      <c r="J22" s="49" t="s">
+        <v>141</v>
+      </c>
+      <c r="K22" s="49">
         <v>1</v>
       </c>
-      <c r="L21" s="50">
+      <c r="L22" s="49">
         <v>30</v>
       </c>
-      <c r="M21" s="22"/>
-    </row>
-    <row r="22" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="45">
-        <f>ROW(B22) - ROW($B$9)</f>
-        <v>13</v>
-      </c>
-      <c r="C22" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="52" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="52" t="s">
-        <v>71</v>
-      </c>
-      <c r="F22" s="52" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22" s="73" t="s">
-        <v>202</v>
-      </c>
-      <c r="H22" s="52" t="s">
-        <v>130</v>
-      </c>
-      <c r="I22" s="63" t="s">
-        <v>171</v>
-      </c>
-      <c r="J22" s="52" t="s">
-        <v>144</v>
-      </c>
-      <c r="K22" s="52">
-        <v>1</v>
-      </c>
-      <c r="L22" s="52">
-        <v>30</v>
-      </c>
-      <c r="M22" s="46"/>
+      <c r="M22" s="45"/>
     </row>
     <row r="23" spans="2:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="45">
+      <c r="B23" s="44">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="50" t="s">
+      <c r="D23" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="50" t="s">
+      <c r="E23" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="F23" s="50" t="s">
+      <c r="F23" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="G23" s="50" t="s">
-        <v>131</v>
-      </c>
-      <c r="H23" s="50" t="s">
-        <v>132</v>
-      </c>
-      <c r="I23" s="50" t="s">
-        <v>172</v>
-      </c>
-      <c r="J23" s="50" t="s">
-        <v>173</v>
-      </c>
-      <c r="K23" s="50">
+      <c r="G23" s="48" t="s">
+        <v>129</v>
+      </c>
+      <c r="H23" s="48" t="s">
+        <v>130</v>
+      </c>
+      <c r="I23" s="48" t="s">
+        <v>169</v>
+      </c>
+      <c r="J23" s="48" t="s">
+        <v>170</v>
+      </c>
+      <c r="K23" s="48">
         <v>1</v>
       </c>
-      <c r="L23" s="50">
+      <c r="L23" s="48">
         <v>28</v>
       </c>
       <c r="M23" s="22"/>
     </row>
     <row r="24" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="45">
-        <f>ROW(B24) - ROW($B$9)</f>
+      <c r="B24" s="44">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="51" t="s">
+      <c r="C24" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="D24" s="52" t="s">
+      <c r="D24" s="74" t="s">
         <v>73</v>
       </c>
-      <c r="E24" s="52" t="s">
+      <c r="E24" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="F24" s="52" t="s">
+      <c r="F24" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="G24" s="62" t="s">
-        <v>203</v>
-      </c>
-      <c r="H24" s="52" t="s">
+      <c r="G24" s="53" t="s">
+        <v>198</v>
+      </c>
+      <c r="H24" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="I24" s="62" t="s">
-        <v>174</v>
-      </c>
-      <c r="J24" s="52" t="s">
-        <v>144</v>
-      </c>
-      <c r="K24" s="52">
+      <c r="I24" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="J24" s="49" t="s">
+        <v>141</v>
+      </c>
+      <c r="K24" s="49">
         <v>1</v>
       </c>
-      <c r="L24" s="52">
+      <c r="L24" s="49">
         <v>50</v>
       </c>
       <c r="M24" s="25"/>
     </row>
     <row r="25" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="45">
+      <c r="B25" s="44">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="49" t="s">
+      <c r="C25" s="80" t="s">
         <v>75</v>
       </c>
-      <c r="D25" s="50" t="s">
+      <c r="D25" s="73" t="s">
         <v>76</v>
       </c>
-      <c r="E25" s="50" t="s">
+      <c r="E25" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="F25" s="50" t="s">
+      <c r="F25" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="G25" s="74" t="s">
-        <v>204</v>
-      </c>
-      <c r="H25" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="I25" s="64" t="s">
-        <v>175</v>
-      </c>
-      <c r="J25" s="50" t="s">
-        <v>144</v>
-      </c>
-      <c r="K25" s="50">
+      <c r="G25" s="63" t="s">
+        <v>199</v>
+      </c>
+      <c r="H25" s="48" t="s">
+        <v>131</v>
+      </c>
+      <c r="I25" s="55" t="s">
+        <v>172</v>
+      </c>
+      <c r="J25" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="K25" s="48">
         <v>6</v>
       </c>
-      <c r="L25" s="50">
+      <c r="L25" s="48">
         <v>160</v>
       </c>
       <c r="M25" s="22"/>
     </row>
     <row r="26" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="45">
-        <f>ROW(B26) - ROW($B$9)</f>
+      <c r="B26" s="44">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="51" t="s">
+      <c r="C26" s="81" t="s">
         <v>41</v>
       </c>
-      <c r="D26" s="52" t="s">
+      <c r="D26" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="E26" s="52" t="s">
+      <c r="E26" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="F26" s="52" t="s">
+      <c r="F26" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="G26" s="65" t="s">
-        <v>205</v>
-      </c>
-      <c r="H26" s="52" t="s">
-        <v>134</v>
-      </c>
-      <c r="I26" s="65" t="s">
-        <v>176</v>
-      </c>
-      <c r="J26" s="52" t="s">
-        <v>177</v>
-      </c>
-      <c r="K26" s="52">
+      <c r="G26" s="56" t="s">
+        <v>200</v>
+      </c>
+      <c r="H26" s="49" t="s">
+        <v>132</v>
+      </c>
+      <c r="I26" s="56" t="s">
+        <v>173</v>
+      </c>
+      <c r="J26" s="49" t="s">
+        <v>174</v>
+      </c>
+      <c r="K26" s="49">
         <v>2</v>
       </c>
-      <c r="L26" s="52">
+      <c r="L26" s="49">
         <v>60</v>
       </c>
       <c r="M26" s="25"/>
     </row>
     <row r="27" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="45">
+      <c r="B27" s="44">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="49" t="s">
+      <c r="C27" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="50" t="s">
+      <c r="D27" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="E27" s="50" t="s">
+      <c r="E27" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="F27" s="50" t="s">
+      <c r="F27" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="G27" s="74" t="s">
-        <v>206</v>
-      </c>
-      <c r="H27" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="I27" s="66" t="s">
+      <c r="G27" s="63" t="s">
+        <v>201</v>
+      </c>
+      <c r="H27" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="I27" s="57" t="s">
+        <v>175</v>
+      </c>
+      <c r="J27" s="48" t="s">
+        <v>176</v>
+      </c>
+      <c r="K27" s="48">
+        <v>1</v>
+      </c>
+      <c r="L27" s="48">
+        <v>50</v>
+      </c>
+      <c r="M27" s="22"/>
+    </row>
+    <row r="28" spans="2:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="44">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C28" s="81" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" s="74" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="49" t="s">
+        <v>85</v>
+      </c>
+      <c r="F28" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="G28" s="49" t="s">
+        <v>134</v>
+      </c>
+      <c r="H28" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="I28" s="49" t="s">
+        <v>177</v>
+      </c>
+      <c r="J28" s="49" t="s">
         <v>178</v>
       </c>
-      <c r="J27" s="50" t="s">
-        <v>179</v>
-      </c>
-      <c r="K27" s="50">
-        <v>1</v>
-      </c>
-      <c r="L27" s="50">
-        <v>50</v>
-      </c>
-      <c r="M27" s="22"/>
-    </row>
-    <row r="28" spans="2:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="45">
-        <f>ROW(B28) - ROW($B$9)</f>
-        <v>19</v>
-      </c>
-      <c r="C28" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="52" t="s">
-        <v>84</v>
-      </c>
-      <c r="E28" s="52" t="s">
-        <v>85</v>
-      </c>
-      <c r="F28" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="G28" s="52" t="s">
-        <v>136</v>
-      </c>
-      <c r="H28" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="I28" s="52" t="s">
-        <v>180</v>
-      </c>
-      <c r="J28" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="K28" s="52">
+      <c r="K28" s="49">
         <v>11</v>
       </c>
-      <c r="L28" s="52">
+      <c r="L28" s="49">
         <v>300</v>
       </c>
       <c r="M28" s="25"/>
     </row>
-    <row r="29" spans="2:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="45">
+    <row r="29" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="44">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="49" t="s">
+      <c r="C29" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="D29" s="50" t="s">
-        <v>86</v>
-      </c>
-      <c r="E29" s="50" t="s">
+      <c r="D29" s="77" t="s">
+        <v>203</v>
+      </c>
+      <c r="E29" s="48" t="s">
+        <v>204</v>
+      </c>
+      <c r="F29" s="48" t="s">
+        <v>80</v>
+      </c>
+      <c r="G29" s="48" t="s">
+        <v>205</v>
+      </c>
+      <c r="H29" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="I29" s="48" t="s">
+        <v>209</v>
+      </c>
+      <c r="J29" s="48" t="s">
+        <v>210</v>
+      </c>
+      <c r="K29" s="47">
+        <v>1</v>
+      </c>
+      <c r="L29" s="48">
+        <v>100</v>
+      </c>
+      <c r="M29" s="22"/>
+    </row>
+    <row r="30" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="44">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C30" s="81" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="74" t="s">
         <v>87</v>
       </c>
-      <c r="F29" s="50" t="s">
+      <c r="E30" s="49" t="s">
+        <v>206</v>
+      </c>
+      <c r="F30" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="G29" s="50" t="s">
-        <v>137</v>
-      </c>
-      <c r="H29" s="50" t="s">
-        <v>25</v>
-      </c>
-      <c r="I29" s="50" t="s">
-        <v>182</v>
-      </c>
-      <c r="J29" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="K29" s="50">
-        <v>13</v>
-      </c>
-      <c r="L29" s="50">
-        <v>400</v>
-      </c>
-      <c r="M29" s="22"/>
-    </row>
-    <row r="30" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="45">
-        <f>ROW(B30) - ROW($B$9)</f>
-        <v>21</v>
-      </c>
-      <c r="C30" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="D30" s="52" t="s">
-        <v>88</v>
-      </c>
-      <c r="E30" s="52" t="s">
-        <v>89</v>
-      </c>
-      <c r="F30" s="52" t="s">
-        <v>80</v>
-      </c>
-      <c r="G30" s="52" t="s">
-        <v>138</v>
-      </c>
-      <c r="H30" s="52" t="s">
-        <v>25</v>
-      </c>
-      <c r="I30" s="62" t="s">
-        <v>183</v>
-      </c>
-      <c r="J30" s="52" t="s">
-        <v>184</v>
-      </c>
-      <c r="K30" s="52">
+      <c r="G30" s="49" t="s">
+        <v>206</v>
+      </c>
+      <c r="H30" s="49" t="s">
+        <v>141</v>
+      </c>
+      <c r="I30" s="53" t="s">
+        <v>141</v>
+      </c>
+      <c r="J30" s="49" t="s">
+        <v>141</v>
+      </c>
+      <c r="K30" s="49">
         <v>1</v>
       </c>
-      <c r="L30" s="52">
-        <v>100</v>
+      <c r="L30" s="49" t="s">
+        <v>141</v>
       </c>
       <c r="M30" s="25"/>
     </row>
-    <row r="31" spans="2:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="45">
+    <row r="31" spans="2:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="44">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="49" t="s">
+      <c r="C31" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="50" t="s">
-        <v>90</v>
-      </c>
-      <c r="E31" s="50" t="s">
-        <v>91</v>
-      </c>
-      <c r="F31" s="50" t="s">
+      <c r="D31" s="48" t="s">
+        <v>207</v>
+      </c>
+      <c r="E31" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F31" s="48" t="s">
         <v>80</v>
       </c>
-      <c r="G31" s="50" t="s">
-        <v>139</v>
-      </c>
-      <c r="H31" s="50" t="s">
-        <v>140</v>
-      </c>
-      <c r="I31" s="50" t="s">
-        <v>185</v>
-      </c>
-      <c r="J31" s="50" t="s">
-        <v>186</v>
-      </c>
-      <c r="K31" s="50">
+      <c r="G31" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="H31" s="48" t="s">
+        <v>25</v>
+      </c>
+      <c r="I31" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="J31" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="K31" s="48">
+        <v>12</v>
+      </c>
+      <c r="L31" s="48">
+        <v>400</v>
+      </c>
+      <c r="M31" s="22"/>
+    </row>
+    <row r="32" spans="2:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="44">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="C32" s="81" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="E32" s="49" t="s">
+        <v>89</v>
+      </c>
+      <c r="F32" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="G32" s="49" t="s">
+        <v>136</v>
+      </c>
+      <c r="H32" s="49" t="s">
+        <v>137</v>
+      </c>
+      <c r="I32" s="49" t="s">
+        <v>180</v>
+      </c>
+      <c r="J32" s="49" t="s">
+        <v>181</v>
+      </c>
+      <c r="K32" s="49">
         <v>1</v>
       </c>
-      <c r="L31" s="50">
+      <c r="L32" s="49">
         <v>50</v>
       </c>
-      <c r="M31" s="22"/>
-    </row>
-    <row r="32" spans="2:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="45">
-        <f>ROW(B32) - ROW($B$9)</f>
-        <v>23</v>
-      </c>
-      <c r="C32" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="D32" s="52" t="s">
-        <v>92</v>
-      </c>
-      <c r="E32" s="52" t="s">
-        <v>93</v>
-      </c>
-      <c r="F32" s="52" t="s">
-        <v>94</v>
-      </c>
-      <c r="G32" s="52" t="s">
-        <v>141</v>
-      </c>
-      <c r="H32" s="52" t="s">
-        <v>142</v>
-      </c>
-      <c r="I32" s="52" t="s">
-        <v>187</v>
-      </c>
-      <c r="J32" s="52" t="s">
-        <v>188</v>
-      </c>
-      <c r="K32" s="52">
-        <v>1</v>
-      </c>
-      <c r="L32" s="52">
-        <v>28</v>
-      </c>
       <c r="M32" s="25"/>
     </row>
-    <row r="33" spans="2:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="45">
+    <row r="33" spans="2:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="44">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="49" t="s">
+      <c r="C33" s="80" t="s">
         <v>41</v>
       </c>
-      <c r="D33" s="50" t="s">
-        <v>95</v>
-      </c>
-      <c r="E33" s="50" t="s">
-        <v>96</v>
-      </c>
-      <c r="F33" s="50" t="s">
+      <c r="D33" s="48" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33" s="48" t="s">
+        <v>91</v>
+      </c>
+      <c r="F33" s="48" t="s">
+        <v>92</v>
+      </c>
+      <c r="G33" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="H33" s="48" t="s">
+        <v>139</v>
+      </c>
+      <c r="I33" s="48" t="s">
+        <v>182</v>
+      </c>
+      <c r="J33" s="48" t="s">
+        <v>183</v>
+      </c>
+      <c r="K33" s="48">
+        <v>1</v>
+      </c>
+      <c r="L33" s="48">
+        <v>28</v>
+      </c>
+      <c r="M33" s="22"/>
+    </row>
+    <row r="34" spans="2:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="44">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C34" s="81" t="s">
+        <v>41</v>
+      </c>
+      <c r="D34" s="49" t="s">
+        <v>93</v>
+      </c>
+      <c r="E34" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="F34" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="G33" s="50" t="s">
-        <v>143</v>
-      </c>
-      <c r="H33" s="50" t="s">
+      <c r="G34" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="H34" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="I33" s="50" t="s">
-        <v>189</v>
-      </c>
-      <c r="J33" s="50" t="s">
-        <v>190</v>
-      </c>
-      <c r="K33" s="50">
+      <c r="I34" s="49" t="s">
+        <v>184</v>
+      </c>
+      <c r="J34" s="49" t="s">
+        <v>185</v>
+      </c>
+      <c r="K34" s="49">
         <v>1</v>
       </c>
-      <c r="L33" s="50">
+      <c r="L34" s="49">
         <v>100</v>
       </c>
-      <c r="M33" s="22"/>
-    </row>
-    <row r="34" spans="2:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="45">
-        <f>ROW(B34) - ROW($B$9)</f>
-        <v>25</v>
-      </c>
-      <c r="C34" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="D34" s="57" t="s">
-        <v>98</v>
-      </c>
-      <c r="E34" s="57" t="s">
-        <v>18</v>
-      </c>
-      <c r="F34" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="G34" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="H34" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="I34" s="67" t="s">
-        <v>144</v>
-      </c>
-      <c r="J34" s="57" t="s">
-        <v>144</v>
-      </c>
-      <c r="K34" s="57">
-        <v>1</v>
-      </c>
-      <c r="L34" s="57" t="s">
-        <v>144</v>
-      </c>
       <c r="M34" s="25"/>
     </row>
     <row r="35" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="45">
+      <c r="B35" s="44">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="49" t="s">
+      <c r="C35" s="83" t="s">
+        <v>95</v>
+      </c>
+      <c r="D35" s="76" t="s">
+        <v>96</v>
+      </c>
+      <c r="E35" s="76" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="76" t="s">
+        <v>34</v>
+      </c>
+      <c r="G35" s="76" t="s">
+        <v>141</v>
+      </c>
+      <c r="H35" s="76" t="s">
+        <v>141</v>
+      </c>
+      <c r="I35" s="78" t="s">
+        <v>141</v>
+      </c>
+      <c r="J35" s="76" t="s">
+        <v>141</v>
+      </c>
+      <c r="K35" s="76">
+        <v>1</v>
+      </c>
+      <c r="L35" s="76" t="s">
+        <v>141</v>
+      </c>
+      <c r="M35" s="22"/>
+    </row>
+    <row r="36" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="44">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="C36" s="81" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="E36" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="D35" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="E35" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="F35" s="50" t="s">
+      <c r="F36" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="50" t="s">
-        <v>145</v>
-      </c>
-      <c r="H35" s="50" t="s">
-        <v>146</v>
-      </c>
-      <c r="I35" s="61" t="s">
-        <v>191</v>
-      </c>
-      <c r="J35" s="50" t="s">
-        <v>144</v>
-      </c>
-      <c r="K35" s="50">
+      <c r="G36" s="49" t="s">
+        <v>142</v>
+      </c>
+      <c r="H36" s="49" t="s">
+        <v>143</v>
+      </c>
+      <c r="I36" s="53" t="s">
+        <v>186</v>
+      </c>
+      <c r="J36" s="49" t="s">
+        <v>141</v>
+      </c>
+      <c r="K36" s="49">
         <v>1</v>
       </c>
-      <c r="L35" s="50">
+      <c r="L36" s="49">
         <v>28</v>
       </c>
-      <c r="M35" s="22"/>
-    </row>
-    <row r="36" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="45">
-        <f>ROW(B36) - ROW($B$9)</f>
-        <v>27</v>
-      </c>
-      <c r="C36" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="D36" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="E36" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="F36" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="G36" s="52" t="s">
-        <v>147</v>
-      </c>
-      <c r="H36" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="I36" s="62" t="s">
-        <v>192</v>
-      </c>
-      <c r="J36" s="52" t="s">
-        <v>144</v>
-      </c>
-      <c r="K36" s="52">
-        <v>1</v>
-      </c>
-      <c r="L36" s="52">
-        <v>27</v>
-      </c>
       <c r="M36" s="25"/>
     </row>
     <row r="37" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="45">
+      <c r="B37" s="44">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="49" t="s">
+      <c r="C37" s="80" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="48" t="s">
+        <v>101</v>
+      </c>
+      <c r="F37" s="48" t="s">
         <v>102</v>
       </c>
-      <c r="D37" s="50" t="s">
+      <c r="G37" s="48" t="s">
+        <v>144</v>
+      </c>
+      <c r="H37" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="I37" s="52" t="s">
+        <v>187</v>
+      </c>
+      <c r="J37" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="K37" s="48">
+        <v>1</v>
+      </c>
+      <c r="L37" s="48">
+        <v>27</v>
+      </c>
+      <c r="M37" s="22"/>
+    </row>
+    <row r="38" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="44">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C38" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="D38" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="E37" s="50" t="s">
-        <v>105</v>
-      </c>
-      <c r="F37" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="G37" s="50" t="s">
-        <v>148</v>
-      </c>
-      <c r="H37" s="50" t="s">
+      <c r="E38" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="F38" s="49" t="s">
+        <v>104</v>
+      </c>
+      <c r="G38" s="49" t="s">
+        <v>145</v>
+      </c>
+      <c r="H38" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="I37" s="61" t="s">
-        <v>193</v>
-      </c>
-      <c r="J37" s="50" t="s">
-        <v>144</v>
-      </c>
-      <c r="K37" s="50">
+      <c r="I38" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="J38" s="49" t="s">
+        <v>141</v>
+      </c>
+      <c r="K38" s="49">
         <v>1</v>
       </c>
-      <c r="L37" s="50">
+      <c r="L38" s="49">
         <v>27</v>
       </c>
-      <c r="M37" s="22"/>
-    </row>
-    <row r="38" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="45">
-        <f>ROW(B38) - ROW($B$9)</f>
-        <v>29</v>
-      </c>
-      <c r="C38" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="D38" s="52" t="s">
-        <v>16</v>
-      </c>
-      <c r="E38" s="52" t="s">
-        <v>107</v>
-      </c>
-      <c r="F38" s="52" t="s">
-        <v>108</v>
-      </c>
-      <c r="G38" s="52" t="s">
-        <v>149</v>
-      </c>
-      <c r="H38" s="52" t="s">
-        <v>27</v>
-      </c>
-      <c r="I38" s="62" t="s">
-        <v>194</v>
-      </c>
-      <c r="J38" s="52" t="s">
-        <v>144</v>
-      </c>
-      <c r="K38" s="52">
-        <v>1</v>
-      </c>
-      <c r="L38" s="52">
-        <v>27</v>
-      </c>
       <c r="M38" s="25"/>
     </row>
     <row r="39" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="45">
+      <c r="B39" s="44">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="C39" s="49" t="s">
+      <c r="C39" s="80" t="s">
+        <v>100</v>
+      </c>
+      <c r="D39" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="48" t="s">
+        <v>105</v>
+      </c>
+      <c r="F39" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="G39" s="48" t="s">
+        <v>146</v>
+      </c>
+      <c r="H39" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="I39" s="52" t="s">
+        <v>189</v>
+      </c>
+      <c r="J39" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="K39" s="48">
+        <v>1</v>
+      </c>
+      <c r="L39" s="48">
+        <v>27</v>
+      </c>
+      <c r="M39" s="22"/>
+    </row>
+    <row r="40" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="44">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="D39" s="50" t="s">
+      <c r="D40" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="E40" s="49" t="s">
+        <v>108</v>
+      </c>
+      <c r="F40" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="G40" s="49" t="s">
+        <v>147</v>
+      </c>
+      <c r="H40" s="49" t="s">
+        <v>148</v>
+      </c>
+      <c r="I40" s="53" t="s">
+        <v>190</v>
+      </c>
+      <c r="J40" s="49" t="s">
+        <v>141</v>
+      </c>
+      <c r="K40" s="49">
+        <v>1</v>
+      </c>
+      <c r="L40" s="49">
+        <v>30</v>
+      </c>
+      <c r="M40" s="22"/>
+    </row>
+    <row r="41" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="44">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C41" s="84" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="85" t="s">
         <v>109</v>
       </c>
-      <c r="E39" s="50" t="s">
+      <c r="E41" s="85" t="s">
         <v>110</v>
       </c>
-      <c r="F39" s="50" t="s">
+      <c r="F41" s="85" t="s">
         <v>34</v>
       </c>
-      <c r="G39" s="50" t="s">
-        <v>150</v>
-      </c>
-      <c r="H39" s="50" t="s">
-        <v>151</v>
-      </c>
-      <c r="I39" s="61" t="s">
-        <v>195</v>
-      </c>
-      <c r="J39" s="50" t="s">
-        <v>144</v>
-      </c>
-      <c r="K39" s="50">
+      <c r="G41" s="86" t="s">
+        <v>208</v>
+      </c>
+      <c r="H41" s="85" t="s">
+        <v>149</v>
+      </c>
+      <c r="I41" s="87" t="s">
+        <v>191</v>
+      </c>
+      <c r="J41" s="85" t="s">
+        <v>192</v>
+      </c>
+      <c r="K41" s="85">
         <v>1</v>
       </c>
-      <c r="L39" s="50">
+      <c r="L41" s="85">
         <v>30</v>
       </c>
-      <c r="M39" s="22"/>
-    </row>
-    <row r="40" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="45">
-        <f>ROW(B40) - ROW($B$9)</f>
-        <v>31</v>
-      </c>
-      <c r="C40" s="58" t="s">
-        <v>42</v>
-      </c>
-      <c r="D40" s="59" t="s">
-        <v>111</v>
-      </c>
-      <c r="E40" s="59" t="s">
-        <v>112</v>
-      </c>
-      <c r="F40" s="59" t="s">
-        <v>34</v>
-      </c>
-      <c r="G40" s="52" t="s">
-        <v>207</v>
-      </c>
-      <c r="H40" s="59" t="s">
-        <v>152</v>
-      </c>
-      <c r="I40" s="68" t="s">
-        <v>196</v>
-      </c>
-      <c r="J40" s="59" t="s">
-        <v>197</v>
-      </c>
-      <c r="K40" s="59">
-        <v>1</v>
-      </c>
-      <c r="L40" s="59">
-        <v>30</v>
-      </c>
-      <c r="M40" s="25"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B41" s="30"/>
-      <c r="C41" s="43"/>
-      <c r="D41" s="31" t="s">
+      <c r="M41" s="88"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B42" s="30"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="E41" s="32"/>
-      <c r="F41" s="33"/>
-      <c r="G41" s="79"/>
-      <c r="H41" s="79"/>
-      <c r="I41" s="79"/>
-      <c r="J41" s="79"/>
-      <c r="K41" s="79"/>
-      <c r="L41" s="79"/>
-      <c r="M41" s="80"/>
-    </row>
-    <row r="42" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="20"/>
-      <c r="C42" s="44"/>
-      <c r="D42" s="7" t="s">
+      <c r="E42" s="32"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="68"/>
+      <c r="H42" s="68"/>
+      <c r="I42" s="68"/>
+      <c r="J42" s="68"/>
+      <c r="K42" s="68"/>
+      <c r="L42" s="68"/>
+      <c r="M42" s="69"/>
+    </row>
+    <row r="43" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="20"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="81"/>
-      <c r="H42" s="81"/>
-      <c r="I42" s="81"/>
-      <c r="J42" s="81"/>
-      <c r="K42" s="81"/>
-      <c r="L42" s="81"/>
-      <c r="M42" s="82"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="70"/>
+      <c r="H43" s="70"/>
+      <c r="I43" s="70"/>
+      <c r="J43" s="70"/>
+      <c r="K43" s="70"/>
+      <c r="L43" s="70"/>
+      <c r="M43" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="M3:M8"/>
     <mergeCell ref="K2:M2"/>
-    <mergeCell ref="G41:M42"/>
+    <mergeCell ref="G42:M43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
